--- a/Copy of contactsDemo-Mainsheet_Macro.xlsx
+++ b/Copy of contactsDemo-Mainsheet_Macro.xlsx
@@ -1,44 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Akash\Desktop\WhatsappBot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34221B50-B54B-498B-B622-DF8084C5A89F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!#REF!</definedName>
   </definedNames>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="6">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>PhoneNumber</t>
+  </si>
+  <si>
+    <t>Remark</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>InvalidNumber</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -68,20 +77,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -119,7 +136,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -191,7 +208,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -223,16 +240,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -354,562 +375,527 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C63"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10.8984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>PhoneNumber</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Remark</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2">
         <v>9899090792</v>
       </c>
-      <c r="C2" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>8928095160</v>
       </c>
-      <c r="C3" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>918943108000</v>
       </c>
-      <c r="C4" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>9846669112</v>
       </c>
-      <c r="C5" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>919895226713</v>
       </c>
-      <c r="C6" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>919846684555</v>
       </c>
-      <c r="C7" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="C7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>9284241810</v>
       </c>
-      <c r="C8" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>9837185985</v>
       </c>
-      <c r="C9" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>9960915577</v>
       </c>
-      <c r="C10" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="C10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>9600399730</v>
       </c>
-      <c r="C11" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="C11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>9497610786</v>
       </c>
-      <c r="C12" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="C12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>9866840427</v>
       </c>
-      <c r="C13" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="C13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>97864508</v>
       </c>
-      <c r="C14" t="str">
-        <v>InvalidNumber</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="C14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>9492938076</v>
       </c>
-      <c r="C15" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="C15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>9844123435</v>
       </c>
-      <c r="C16" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="C16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>7904882542</v>
       </c>
-      <c r="C17" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="C17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>9944066778</v>
       </c>
-      <c r="C18" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="C18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>9496537485</v>
       </c>
-      <c r="C19" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="C19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>9971726845</v>
       </c>
-      <c r="C20" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="C20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>9903031582</v>
       </c>
-      <c r="C21" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="C21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>9323150379</v>
       </c>
-      <c r="C22" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="C22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>9999010544</v>
       </c>
-      <c r="C23" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="C23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>9656277555</v>
       </c>
-      <c r="C24" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="C24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>9899270074</v>
       </c>
-      <c r="C25" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="26">
+      <c r="C25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>8390108833</v>
       </c>
-      <c r="C26" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="27">
+      <c r="C26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>9600363926</v>
       </c>
-      <c r="C27" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="28">
+      <c r="C27" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>9829011781</v>
       </c>
-      <c r="C28" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="29">
+      <c r="C28" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>9968000000</v>
       </c>
-      <c r="C29" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="30">
+      <c r="C29" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>9548502855</v>
       </c>
-      <c r="C30" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="31">
+      <c r="C30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>8574070227</v>
       </c>
-      <c r="C31" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="32">
+      <c r="C31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>9980305500</v>
       </c>
-      <c r="C32" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="33">
+      <c r="C32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>9841885065</v>
       </c>
-      <c r="C33" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="34">
+      <c r="C33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>8489999882</v>
       </c>
-      <c r="C34" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="35">
+      <c r="C34" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>7736021888</v>
       </c>
-      <c r="C35" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="36">
+      <c r="C35" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>8459162902</v>
       </c>
-      <c r="C36" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="37">
+      <c r="C36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>8970117254</v>
       </c>
-      <c r="C37" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="C37" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>8754849026</v>
       </c>
-      <c r="C38" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="39">
+      <c r="C38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>7907258501</v>
       </c>
-      <c r="C39" t="str">
-        <v>Failed</v>
-      </c>
-    </row>
-    <row r="40">
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>9860929801</v>
       </c>
-      <c r="C40" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="41">
+      <c r="C40" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>9011411321</v>
       </c>
-      <c r="C41" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="42">
+      <c r="C41" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>8007986000</v>
       </c>
-      <c r="C42" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="43">
+      <c r="C42" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>9578810504</v>
       </c>
-      <c r="C43" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="44">
+      <c r="C43" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>9971140003</v>
       </c>
-      <c r="C44" t="str">
-        <v>Failed</v>
-      </c>
-    </row>
-    <row r="45">
+      <c r="C44" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>8847794097</v>
       </c>
-      <c r="C45" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="46">
+      <c r="C45" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>7838912792</v>
       </c>
-      <c r="C46" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="47">
+      <c r="C46" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>9030271841</v>
       </c>
-      <c r="C47" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="48">
+      <c r="C47" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>9372396434</v>
       </c>
-      <c r="C48" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="49">
+      <c r="C48" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>7760757272</v>
       </c>
-      <c r="C49" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="50">
+      <c r="C49" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>9578375939</v>
       </c>
-      <c r="C50" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="51">
+      <c r="C50" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>9816839949</v>
       </c>
-      <c r="C51" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="52">
+      <c r="C51" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>9215966670</v>
       </c>
-      <c r="C52" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="53">
+      <c r="C52" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>9566658376</v>
       </c>
-      <c r="C53" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="54">
+      <c r="C53" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>9074737174</v>
       </c>
-      <c r="C54" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="55">
+      <c r="C54" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>9921222444</v>
       </c>
-      <c r="C55" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="56">
+      <c r="C55" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>9944886969</v>
       </c>
-      <c r="C56" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="57">
+      <c r="C56" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>9811015116</v>
       </c>
-      <c r="C57" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="58">
+      <c r="C57" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>9865921007</v>
       </c>
-      <c r="C58" t="str">
-        <v>Done</v>
-      </c>
-    </row>
-    <row r="59">
+      <c r="C58" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>7358504100</v>
       </c>
-      <c r="C59" t="str">
-        <v>Failed</v>
-      </c>
-    </row>
-    <row r="60">
+      <c r="C59" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>9908072065</v>
       </c>
-      <c r="C60" t="str">
-        <v>Failed</v>
-      </c>
-    </row>
-    <row r="61">
+      <c r="C60" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>9814166767</v>
       </c>
-      <c r="C61" t="str">
-        <v>Failed</v>
-      </c>
-    </row>
-    <row r="62">
+      <c r="C61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>9989723097</v>
       </c>
-      <c r="C62" t="str">
-        <v>Failed</v>
-      </c>
-    </row>
-    <row r="63">
+      <c r="C62" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B63">
-        <v>9893415975</v>
+        <v>7030369545</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C63"/>
+    <ignoredError sqref="A1:C62 A63 C63" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>